--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013857</v>
+        <v>127013832</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504399</v>
+        <v>504582</v>
       </c>
       <c r="R3" t="n">
-        <v>7141089</v>
+        <v>7141218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013832</v>
+        <v>127013833</v>
       </c>
       <c r="B4" t="n">
         <v>57657</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504582</v>
+        <v>504566</v>
       </c>
       <c r="R4" t="n">
-        <v>7141218</v>
+        <v>7141208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013833</v>
+        <v>127013857</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,16 +1011,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504566</v>
+        <v>504399</v>
       </c>
       <c r="R5" t="n">
-        <v>7141208</v>
+        <v>7141089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013832</v>
+        <v>127013857</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504582</v>
+        <v>504399</v>
       </c>
       <c r="R3" t="n">
-        <v>7141218</v>
+        <v>7141089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013833</v>
+        <v>127013832</v>
       </c>
       <c r="B4" t="n">
         <v>57657</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504566</v>
+        <v>504582</v>
       </c>
       <c r="R4" t="n">
-        <v>7141208</v>
+        <v>7141218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013857</v>
+        <v>127013833</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,16 +1011,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504399</v>
+        <v>504566</v>
       </c>
       <c r="R5" t="n">
-        <v>7141089</v>
+        <v>7141208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -898,27 +898,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013832</v>
+        <v>127013873</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -926,17 +926,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Risede, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504582</v>
+        <v>504583</v>
       </c>
       <c r="R4" t="n">
-        <v>7141218</v>
+        <v>7141179</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,11 +981,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013833</v>
+        <v>127013832</v>
       </c>
       <c r="B5" t="n">
         <v>57657</v>
@@ -1035,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504566</v>
+        <v>504582</v>
       </c>
       <c r="R5" t="n">
-        <v>7141208</v>
+        <v>7141218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1082,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013831</v>
+        <v>127013833</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1137,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504579</v>
+        <v>504566</v>
       </c>
       <c r="R6" t="n">
-        <v>7141222</v>
+        <v>7141208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,27 +1211,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013873</v>
+        <v>127013831</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1232,29 +1239,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Risede, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504583</v>
+        <v>504579</v>
       </c>
       <c r="R7" t="n">
-        <v>7141179</v>
+        <v>7141222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,6 +1282,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127013857</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127013873</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>57765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>127013832</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127013833</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>127013831</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127013857</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127013873</v>
       </c>
       <c r="B4" t="n">
-        <v>57765</v>
+        <v>57767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>127013832</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127013833</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>127013831</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013832</v>
+        <v>127013833</v>
       </c>
       <c r="B5" t="n">
         <v>57663</v>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504582</v>
+        <v>504566</v>
       </c>
       <c r="R5" t="n">
-        <v>7141218</v>
+        <v>7141208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013833</v>
+        <v>127013832</v>
       </c>
       <c r="B6" t="n">
         <v>57663</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504566</v>
+        <v>504582</v>
       </c>
       <c r="R6" t="n">
-        <v>7141208</v>
+        <v>7141218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -1007,7 +1007,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013833</v>
+        <v>127013832</v>
       </c>
       <c r="B5" t="n">
         <v>57663</v>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504566</v>
+        <v>504582</v>
       </c>
       <c r="R5" t="n">
-        <v>7141208</v>
+        <v>7141218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013832</v>
+        <v>127013833</v>
       </c>
       <c r="B6" t="n">
         <v>57663</v>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504582</v>
+        <v>504566</v>
       </c>
       <c r="R6" t="n">
-        <v>7141218</v>
+        <v>7141208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>127013873</v>
       </c>
       <c r="B4" t="n">
-        <v>57767</v>
+        <v>57770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>127013832</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127013833</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>127013831</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>127013832</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>127013833</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>127013831</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33887-2025 artfynd.xlsx
+++ b/artfynd/A 33887-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>127013857</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,27 +898,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013873</v>
+        <v>127013832</v>
       </c>
       <c r="B4" t="n">
-        <v>57770</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -926,29 +926,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Risede, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504583</v>
+        <v>504582</v>
       </c>
       <c r="R4" t="n">
-        <v>7141179</v>
+        <v>7141218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,6 +969,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013832</v>
+        <v>127013833</v>
       </c>
       <c r="B5" t="n">
         <v>57672</v>
@@ -1042,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504582</v>
+        <v>504566</v>
       </c>
       <c r="R5" t="n">
-        <v>7141218</v>
+        <v>7141208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1075,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013833</v>
+        <v>127013831</v>
       </c>
       <c r="B6" t="n">
         <v>57672</v>
@@ -1144,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504566</v>
+        <v>504579</v>
       </c>
       <c r="R6" t="n">
-        <v>7141208</v>
+        <v>7141222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,27 +1204,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013831</v>
+        <v>127013873</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1239,17 +1232,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Risede, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504579</v>
+        <v>504583</v>
       </c>
       <c r="R7" t="n">
-        <v>7141222</v>
+        <v>7141179</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,11 +1287,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
